--- a/exercises/Problem1_2.xlsx
+++ b/exercises/Problem1_2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\m_lad\Repos\Mathematics\exercises\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{064E52EF-652B-4505-8060-1E1F76B1CF39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{042476ED-579F-4A87-B01E-A6921C926F32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{80783E05-9B0E-43FE-BFDE-F2BC814AD7DE}"/>
+    <workbookView xWindow="-28800" yWindow="1350" windowWidth="28800" windowHeight="15345" activeTab="1" xr2:uid="{80783E05-9B0E-43FE-BFDE-F2BC814AD7DE}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1333,21 +1333,25 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02F1BCC9-87CD-4143-AEEA-B606FD93F8EF}">
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1">
         <v>3</v>
       </c>
-      <c r="C1">
+      <c r="D1">
         <v>0</v>
       </c>
-      <c r="D1">
+      <c r="E1">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F1">
+        <f>3+3*D1+D1*(D1-1)</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>6</v>
       </c>
@@ -1355,76 +1359,232 @@
         <f>A2-A1</f>
         <v>3</v>
       </c>
-      <c r="C2">
+      <c r="D2">
         <v>1</v>
       </c>
-      <c r="D2">
-        <f>D1+((2*C2)+1)</f>
+      <c r="E2">
+        <f>E1+((2*D2)+1)</f>
         <v>6</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F2">
+        <f t="shared" ref="F2:F11" si="0">3+3*D2+D2*(D2-1)</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>11</v>
       </c>
       <c r="B3">
-        <f t="shared" ref="B3:B6" si="0">A3-A2</f>
+        <f t="shared" ref="B3:B11" si="1">A3-A2</f>
         <v>5</v>
       </c>
       <c r="C3">
+        <f>B3-B2</f>
         <v>2</v>
       </c>
       <c r="D3">
-        <f t="shared" ref="D3:D6" si="1">D2+((2*C3)+1)</f>
+        <v>2</v>
+      </c>
+      <c r="E3">
+        <f t="shared" ref="E3:E11" si="2">E2+((2*D3)+1)</f>
         <v>11</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F3">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>18</v>
       </c>
       <c r="B4">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+      <c r="C4">
+        <f t="shared" ref="C4:C11" si="3">B4-B3</f>
+        <v>2</v>
+      </c>
+      <c r="D4">
+        <v>3</v>
+      </c>
+      <c r="E4">
+        <f t="shared" si="2"/>
+        <v>18</v>
+      </c>
+      <c r="F4">
         <f t="shared" si="0"/>
-        <v>7</v>
-      </c>
-      <c r="C4">
-        <v>3</v>
-      </c>
-      <c r="D4">
-        <f t="shared" si="1"/>
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>27</v>
       </c>
       <c r="B5">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+      <c r="C5">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+      <c r="D5">
+        <v>4</v>
+      </c>
+      <c r="E5">
+        <f t="shared" si="2"/>
+        <v>27</v>
+      </c>
+      <c r="F5">
         <f t="shared" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="C5">
-        <v>4</v>
-      </c>
-      <c r="D5">
-        <f t="shared" si="1"/>
         <v>27</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>38</v>
       </c>
       <c r="B6">
+        <f t="shared" si="1"/>
+        <v>11</v>
+      </c>
+      <c r="C6">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+      <c r="D6">
+        <v>5</v>
+      </c>
+      <c r="E6">
+        <f t="shared" si="2"/>
+        <v>38</v>
+      </c>
+      <c r="F6">
         <f t="shared" si="0"/>
-        <v>11</v>
-      </c>
-      <c r="C6">
-        <v>5</v>
-      </c>
-      <c r="D6">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>51</v>
+      </c>
+      <c r="B7">
         <f t="shared" si="1"/>
-        <v>38</v>
+        <v>13</v>
+      </c>
+      <c r="C7">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+      <c r="D7">
+        <v>6</v>
+      </c>
+      <c r="E7">
+        <f t="shared" si="2"/>
+        <v>51</v>
+      </c>
+      <c r="F7">
+        <f t="shared" si="0"/>
+        <v>51</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>66</v>
+      </c>
+      <c r="B8">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="C8">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+      <c r="D8">
+        <v>7</v>
+      </c>
+      <c r="E8">
+        <f t="shared" si="2"/>
+        <v>66</v>
+      </c>
+      <c r="F8">
+        <f t="shared" si="0"/>
+        <v>66</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>83</v>
+      </c>
+      <c r="B9">
+        <f t="shared" si="1"/>
+        <v>17</v>
+      </c>
+      <c r="C9">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+      <c r="D9">
+        <v>8</v>
+      </c>
+      <c r="E9">
+        <f t="shared" si="2"/>
+        <v>83</v>
+      </c>
+      <c r="F9">
+        <f t="shared" si="0"/>
+        <v>83</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>102</v>
+      </c>
+      <c r="B10">
+        <f t="shared" si="1"/>
+        <v>19</v>
+      </c>
+      <c r="C10">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+      <c r="D10">
+        <v>9</v>
+      </c>
+      <c r="E10">
+        <f t="shared" si="2"/>
+        <v>102</v>
+      </c>
+      <c r="F10">
+        <f t="shared" si="0"/>
+        <v>102</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>123</v>
+      </c>
+      <c r="B11">
+        <f t="shared" si="1"/>
+        <v>21</v>
+      </c>
+      <c r="C11">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+      <c r="D11">
+        <v>10</v>
+      </c>
+      <c r="E11">
+        <f t="shared" si="2"/>
+        <v>123</v>
+      </c>
+      <c r="F11">
+        <f t="shared" si="0"/>
+        <v>123</v>
       </c>
     </row>
   </sheetData>
